--- a/backtest_runs/20260410_193731/by_symbol/SURC/SURC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SURC/SURC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-398.6399999999979</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>99601.36</v>
@@ -587,7 +587,7 @@
         <v>-2138.159999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>97463.2</v>
@@ -679,7 +679,7 @@
         <v>-8362.37999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>92915.08</v>
@@ -1047,7 +1047,7 @@
         <v>-5417.880000000004</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>109884.46</v>
@@ -1093,7 +1093,7 @@
         <v>-2346.53999999999</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>107537.92</v>
@@ -1139,7 +1139,7 @@
         <v>-1494.900000000005</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>106043.02</v>
@@ -1185,7 +1185,7 @@
         <v>-5426.939999999995</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>100616.08</v>
@@ -1231,7 +1231,7 @@
         <v>-1232.159999999999</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>99383.92000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-2491.5</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>96892.42000000001</v>
